--- a/Map.xlsx
+++ b/Map.xlsx
@@ -19,12 +19,25 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t xml:space="preserve">10
+Descendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12
+CrossRoad</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -51,6 +64,18 @@
     </font>
     <font>
       <sz val="22"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -116,24 +141,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -320,7 +353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultColWidth="15.328125" defaultRowHeight="85.05" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="15.32"/>
@@ -355,19 +388,28 @@
         <v>9</v>
       </c>
       <c r="N1" s="2"/>
-      <c r="O1" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="O1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="4"/>
       <c r="G2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="M2" s="4"/>
       <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -376,9 +418,23 @@
       <c r="G3" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="M3" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G4" s="4"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O5" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,10 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14
+No juice</t>
   </si>
   <si>
     <t xml:space="preserve">12
@@ -141,7 +145,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -160,6 +164,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -418,18 +426,25 @@
       <c r="G3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="K3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="O3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="2"/>
       <c r="Q3" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="R3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="O5" s="1" t="n">

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,10 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16
+Paradise</t>
   </si>
   <si>
     <t xml:space="preserve">14
@@ -85,7 +89,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,12 +108,6 @@
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FF99CCFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
@@ -145,7 +143,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -172,10 +170,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -203,7 +197,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -423,17 +417,25 @@
       <c r="A3" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>16</v>
-      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2"/>
       <c r="M3" s="5" t="s">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="1" t="n">
@@ -442,7 +444,13 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G4" s="7"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
     </row>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -355,7 +355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultColWidth="15.328125" defaultRowHeight="85.05" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="15.32"/>
@@ -455,8 +455,19 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M5" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="O5" s="1" t="n">
         <v>15</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O7" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -36,6 +36,22 @@
   <si>
     <t xml:space="preserve">12
 CrossRoad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15
+More</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One way, 
+Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19
+Swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23
+OOOps</t>
   </si>
 </sst>
 </file>
@@ -45,7 +61,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -84,6 +100,13 @@
     </font>
     <font>
       <sz val="15"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -143,7 +166,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -170,6 +193,14 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -355,7 +386,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="15.328125" defaultRowHeight="85.05" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="15.32"/>
@@ -426,7 +457,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="2"/>
@@ -451,6 +482,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="O4" s="2"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
     </row>
@@ -458,17 +490,54 @@
       <c r="M5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="O5" s="1" t="n">
-        <v>15</v>
-      </c>
+      <c r="O5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" s="2"/>
       <c r="Q5" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O7" s="1" t="n">
-        <v>19</v>
-      </c>
+      <c r="M7" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O8" s="8"/>
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -521,9 +521,13 @@
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="O8" s="8"/>
+      <c r="Q8" s="2"/>
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M9" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="O9" s="5" t="s">
         <v>7</v>
       </c>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -40,6 +40,9 @@
   <si>
     <t xml:space="preserve">15
 More</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cannot get up from low ledge</t>
   </si>
   <si>
     <t xml:space="preserve">One way, 
@@ -61,7 +64,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -100,6 +103,12 @@
     </font>
     <font>
       <sz val="15"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -195,12 +204,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -482,14 +491,20 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
       <c r="O4" s="2"/>
+      <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K5" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="M5" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="5" t="s">
         <v>4</v>
       </c>
@@ -500,18 +515,26 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>5</v>
       </c>
+      <c r="O6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K7" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="M7" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="1" t="n">
@@ -520,16 +543,25 @@
       <c r="R7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O8" s="8"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K9" s="1" t="n">
+        <v>28</v>
+      </c>
       <c r="M9" s="1" t="n">
         <v>25</v>
       </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="1" t="n">
@@ -538,6 +570,8 @@
       <c r="R9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -38,6 +38,10 @@
 CrossRoad</t>
   </si>
   <si>
+    <t xml:space="preserve">27
+Mushroom</t>
+  </si>
+  <si>
     <t xml:space="preserve">15
 More</t>
   </si>
@@ -49,8 +53,20 @@
 Down</t>
   </si>
   <si>
+    <t xml:space="preserve">26
+Tears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22
+Return of the</t>
+  </si>
+  <si>
     <t xml:space="preserve">19
 Swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28
+Bottle</t>
   </si>
   <si>
     <t xml:space="preserve">23
@@ -175,7 +191,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,11 +220,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -498,15 +522,19 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K5" s="1" t="n">
-        <v>27</v>
-      </c>
+      <c r="I5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="2"/>
       <c r="M5" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="1" t="n">
@@ -515,26 +543,33 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="O6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>6</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K7" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>22</v>
+      <c r="I7" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="1" t="n">
@@ -543,25 +578,33 @@
       <c r="R7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="8" t="s">
-        <v>6</v>
+      <c r="O8" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K9" s="1" t="n">
-        <v>28</v>
-      </c>
+      <c r="I9" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="2"/>
       <c r="M9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="1" t="n">
@@ -570,6 +613,10 @@
       <c r="R9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -36,6 +36,10 @@
   <si>
     <t xml:space="preserve">12
 CrossRoad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30
+Corner</t>
   </si>
   <si>
     <t xml:space="preserve">27
@@ -522,11 +526,13 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I5" s="1" t="n">
-        <v>30</v>
-      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="2"/>
       <c r="K5" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1" t="n">
@@ -534,7 +540,7 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="1" t="n">
@@ -543,33 +549,38 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H6" s="4"/>
+      <c r="I6" s="2"/>
       <c r="K6" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H7" s="4"/>
       <c r="I7" s="1" t="n">
         <v>31</v>
       </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="5" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L7" s="2"/>
       <c r="M7" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="1" t="n">
@@ -578,25 +589,33 @@
       <c r="R7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H8" s="4"/>
+      <c r="I8" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G9" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1" t="n">
@@ -604,7 +623,7 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="1" t="n">
@@ -613,6 +632,14 @@
       <c r="R9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -566,6 +566,9 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G7" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="H7" s="4"/>
       <c r="I7" s="1" t="n">
         <v>31</v>
@@ -606,6 +609,9 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E9" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="G9" s="1" t="n">
         <v>32</v>
       </c>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -67,6 +67,18 @@
   <si>
     <t xml:space="preserve">19
 Swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38
+Bottom Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35
+Shallow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33
+Low tide</t>
   </si>
   <si>
     <t xml:space="preserve">28
@@ -566,6 +578,15 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="G7" s="1" t="n">
         <v>34</v>
       </c>
@@ -592,6 +613,8 @@
       <c r="R7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C8" s="4"/>
+      <c r="G8" s="2"/>
       <c r="H8" s="4"/>
       <c r="I8" s="9" t="s">
         <v>8</v>
@@ -609,9 +632,18 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="1" t="n">
-        <v>33</v>
-      </c>
+      <c r="A9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="1" t="n">
         <v>32</v>
       </c>
@@ -621,7 +653,7 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1" t="n">
@@ -629,7 +661,7 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="1" t="n">

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -538,6 +538,9 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G5" s="1" t="n">
+        <v>40</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="5" t="s">
         <v>4</v>
@@ -561,6 +564,9 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G6" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="K6" s="8" t="s">
@@ -587,6 +593,7 @@
       <c r="E7" s="1" t="n">
         <v>36</v>
       </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="1" t="n">
         <v>34</v>
       </c>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t xml:space="preserve">10
 Descendum</t>
@@ -55,6 +55,10 @@
   <si>
     <t xml:space="preserve">One way, 
 Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36
+Air</t>
   </si>
   <si>
     <t xml:space="preserve">26
@@ -497,6 +501,12 @@
       <c r="A3" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>44</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="1" t="n">
         <v>6</v>
@@ -524,6 +534,7 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -538,6 +549,16 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="1" t="n">
         <v>40</v>
       </c>
@@ -564,6 +585,11 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="8" t="s">
         <v>7</v>
       </c>
@@ -590,8 +616,9 @@
       <c r="C7" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>36</v>
+      <c r="D7" s="2"/>
+      <c r="E7" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="1" t="n">
@@ -603,15 +630,15 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="1" t="n">
@@ -621,6 +648,7 @@
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="4"/>
+      <c r="E8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="4"/>
       <c r="I8" s="9" t="s">
@@ -640,15 +668,15 @@
     </row>
     <row r="9" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="1" t="n">
@@ -660,7 +688,7 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1" t="n">
@@ -668,7 +696,7 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="1" t="n">

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -587,6 +587,7 @@
     <row r="6" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -613,6 +614,7 @@
       <c r="A7" s="1" t="n">
         <v>39</v>
       </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="1" t="n">
         <v>37</v>
       </c>
@@ -647,6 +649,7 @@
       <c r="R7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
       <c r="C8" s="4"/>
       <c r="E8" s="2"/>
       <c r="G8" s="2"/>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -486,6 +486,7 @@
     <row r="2" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="G2" s="2"/>
       <c r="I2" s="4"/>
@@ -534,6 +535,11 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -552,9 +558,11 @@
       <c r="A5" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="1" t="n">
         <v>41</v>
       </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="1" t="n">
         <v>43</v>
       </c>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -488,6 +488,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="2"/>
       <c r="I2" s="4"/>
       <c r="K2" s="4"/>
@@ -502,13 +503,15 @@
       <c r="A3" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="1" t="n">
         <v>45</v>
       </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="1" t="n">
         <v>6</v>
       </c>

--- a/Map.xlsx
+++ b/Map.xlsx
@@ -511,7 +511,7 @@
       <c r="E3" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="2"/>
       <c r="G3" s="1" t="n">
         <v>6</v>
       </c>
